--- a/artfynd/A 73465-2021 artfynd.xlsx
+++ b/artfynd/A 73465-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73465-2021 artfynd.xlsx
+++ b/artfynd/A 73465-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>98116714</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533909.6156529984</v>
+        <v>533910</v>
       </c>
       <c r="R2" t="n">
-        <v>6357423.428049355</v>
+        <v>6357424</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-01-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98117106</v>
+        <v>109382871</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,36 +784,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Mobäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533934.2842119746</v>
+        <v>533814</v>
       </c>
       <c r="R3" t="n">
-        <v>6357381.557557624</v>
+        <v>6357347</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,22 +844,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-14</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-14</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,52 +886,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98117256</v>
+        <v>113096913</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Mobäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533881.4946805137</v>
+        <v>533775</v>
       </c>
       <c r="R4" t="n">
-        <v>6357360.082667438</v>
+        <v>6357376</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98117177</v>
+        <v>98116951</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533889.494230555</v>
+        <v>533930</v>
       </c>
       <c r="R5" t="n">
-        <v>6357373.095124992</v>
+        <v>6357455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,19 +1059,14 @@
           <t>2022-01-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett 50-tal plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,40 +1093,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98139397</v>
+        <v>98138306</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533920.0583208456</v>
+        <v>533859</v>
       </c>
       <c r="R6" t="n">
-        <v>6357402.477164462</v>
+        <v>6357389</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,19 +1167,9 @@
           <t>2022-01-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-01-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,44 +1196,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98138306</v>
+        <v>98117256</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533858.01449607</v>
+        <v>533881</v>
       </c>
       <c r="R7" t="n">
-        <v>6357389.017370961</v>
+        <v>6357361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,22 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1292,627 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108742946</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mobäckskärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533772</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6357355</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108742882</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mobäckskärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533778</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6357358</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98117106</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>533934</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6357382</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-01-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-01-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>98117177</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533889</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6357374</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-01-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-01-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98139397</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>533920</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6357403</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-01-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-01-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>108742957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mobäckskärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>533772</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6357355</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73465-2021 artfynd.xlsx
+++ b/artfynd/A 73465-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98116714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109382871</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113096913</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98116951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98138306</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98117256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108742946</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108742882</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98117106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98117177</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98139397</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,8 +1973,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108742957</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>